--- a/US-Water-Infrastructure-Analysis.xlsx
+++ b/US-Water-Infrastructure-Analysis.xlsx
@@ -21,7 +21,8 @@
     <sheet name="Ferguson" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Comparison" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Dashboard" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="Sources" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Asset Data Sources" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Sources" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="965">
   <si>
     <t xml:space="preserve">US Water Infrastructure — Analysis Workbook</t>
   </si>
@@ -44,7 +45,7 @@
     <t xml:space="preserve">What this workbook contains</t>
   </si>
   <si>
-    <t xml:space="preserve">A quantitative companion to the written analysis. Fourteen tabs covering who funds US water infrastructure, what annual spend should look like through 2035, the engineering evidence for replacement, and how both flow through to the two listed distributors with direct exposure.</t>
+    <t xml:space="preserve">A quantitative companion to the written analysis. Fifteen tabs covering who funds US water infrastructure, what annual spend should look like through 2035, the engineering evidence for replacement, where the underlying asset data actually lives, and how it all flows through to the two listed distributors with direct exposure.</t>
   </si>
   <si>
     <t xml:space="preserve">Tab</t>
@@ -140,15 +141,21 @@
     <t xml:space="preserve">Side by side plus revenue sensitivity to market growth</t>
   </si>
   <si>
+    <t xml:space="preserve">Asset Data Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where pipe installation year and repair history exist in the public record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources</t>
   </si>
   <si>
     <t xml:space="preserve">Every source with its known interest or bias</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">Colour legend</t>
   </si>
   <si>
@@ -2294,6 +2301,336 @@
     <t xml:space="preserve">VERIFY BEFORE USE: public-sector figures in this workbook were obtained via search results summarising primary documents, because this environment's network policy blocked direct access to cbo.gov, epa.gov, census.gov, congress.gov and fred.stlouisfed.org. Company financials came from Quartr's primary filings and do not carry this caveat. See the Read Me tab.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pipe Age and Repair History — What Is Public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where segment-level installation year and repair history can actually be obtained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The structural gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National age registry?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granularity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publisher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural gas + hazardous liquid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National, by decade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHMSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By-Decade Inventory: mileage by decade of installation for gas distribution, gas transmission and hazardous liquid. Operators must file annual reports covering age, length, diameter, material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water and wastewater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No federal reporting requirement for pipe age. SDWIS carries compliance and violations but no distribution-system asset inventory. Responsibility sits with ~50,000 community water systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSEQUENCE: every national water pipe-age figure in this workbook is a survey estimate, not a census. The USU study covers ~400,000 miles — over 17% of the 2.3m miles in the US and Canada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1 — asset-level and genuinely public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it contains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Examples and caveats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal GIS open-data portals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water main layer: installation year, material, diameter, length, sometimes lining status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipe segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seattle Public Utilities Water Mains (incl. a 'Presumed Unlined' condition layer); Open Data DC; federated search via catalog.data.gov. THE BEST SOURCE FOR PIPE AGE. Install year often null on the oldest segments — precisely the ones that matter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water main break datasets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break location and date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC Water publishes five years of breaks, updated weekly. Records FAILURES, not planned replacement — a segment replaced on schedule generates no record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street opening / excavation permits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who dug, where, when, why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYCStreets permit management; Chicago CDOT Office of Underground Coordination. The best available proxy for LAST PERIOD OF REPAIR, and it captures planned work that break data misses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead service line inventories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service line material by location incl. lead, galvanized-requiring-replacement and unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address / parcel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory public accessibility since 16 Oct 2024; systems &gt;50,000 must publish online. Baseline inventory and replacement plan due 1 Nov 2027, updated ANNUALLY. State dashboards: New York, Minnesota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 — system-level, and the most useful for an investor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal bond official statements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System description: miles of main, material mix, age profile, capital plan, replacement rates, rate history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSRB EMMA — official statements for essentially every muni bond since 1990, plus continuing disclosure. Disclosure liability compels the issuer to describe the asset. HIGHEST-DENSITY PUBLIC SOURCE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset management plans / CIPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment register with material, diameter, install year, replacement value, maintenance history; sequenced CIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published directly by some utilities, e.g. Sacramento Suburban Water District's Distribution Main Asset Management Plan. Availability is patchy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor-owned utility 10-Ks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replacement cycle, miles to be replaced, capital plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Water: renewal rate improved from a 250-year cycle (2009) to ~125-year by 2028; ~2,000 miles 2024-2028; $34-38bn over ten years. An SEC filing, not an advocacy report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State PUC rate-case dockets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation studies with assumed service lives by asset class; plant-in-service vintage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company / asset class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public docket filings, state by state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System condition assessments and dated remediation schedules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOJ/EPA lodged decrees. Effectively a court-supervised published asset plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 3 — national aggregates (estimates, not censuses)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it gives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USU Water Main Break Rates (Dec 2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break rate and age by material; avg failure age 53 yrs; 33% of mains &gt;50 yrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">802 utilities, ~400,000 miles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;17% of the 2.3m miles in US+Canada. Best available, still a sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPA CWNS 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACILITY-LEVEL project and needs data, downloadable CSV or Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All states, 100% participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projects and costs, NOT pipe age. Wastewater only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National and state needs; 9.2m lead service lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregated. Underlying utility responses are not public.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMich Center for Sustainable Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average age of US water pipes 45 years (2020), up from 25 (1970)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived estimate, not a measurement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What does not exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal water analogue to PHMSA By-Decade Inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOES NOT EXIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No agency collects water pipe age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDWIS distribution-system asset inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDWIS covers compliance, violations, enforcement and basic system inventory only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPEiD (Virginia Tech SWIM Center)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXISTS BUT NOT OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bureau of Reclamation funded; data from 500+ US water utilities and 100 federal facilities. A SECURED utility decision-support platform, not an open dataset. Its existence is the clearest evidence the gap is real and recognised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWIA s.2013 risk and resilience assessments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIDENTIAL BY STATUTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliberately withheld on security grounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipe for a bottom-up demand estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select the 20-30 utilities with the largest capital programmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifiable from EMMA issuance volume and CWNS project data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull each water main GIS layer; build a vintage histogram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miles by installation decade and material; implied replacement rate from year-on-year layer changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull the EMMA official statement and CIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stated forward capital plan; continuing disclosure gives actuals vs plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull the LSL inventory, and from Nov 2027 the annual replacement plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service line counts and realised replacement pace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull break datasets and street-opening permits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validation that stated replacement is physically happening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITATIONS. Coverage skews to large, well-resourced utilities — most of the ~50,000 community water systems publish nothing, so extrapolating from the transparent ones overstates system quality and understates need. Installation year is frequently null on the oldest segments. 'Last repair' is almost never an attribute — breaks and permits are proxies, and both miss trenchless rehabilitation such as CIPP lining and pipe bursting. Schemas are not standardised across utilities, which is the specific problem PIPEiD exists to solve and has not solved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFICATION CAVEAT: none of these portals could be opened from the session that produced this workbook — the environment's egress allowlist blocks all external hosts. Descriptions are built from search evidence about what these sources contain, not from inspecting them. Confirm each dataset's actual schema, and how sparsely the installation-year field is populated, before relying on it.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources and Known Biases</t>
   </si>
   <si>
@@ -2301,9 +2638,6 @@
   </si>
   <si>
     <t xml:space="preserve">Public spending — historical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publisher</t>
   </si>
   <si>
     <t xml:space="preserve">Document</t>
@@ -3218,7 +3552,7 @@
     <tabColor rgb="FF1F3B52"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3241,7 +3575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -3400,109 +3734,120 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C21" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="5" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="10" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="C28" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+    <row r="31" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+    <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+    <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+    <row r="38" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+    <row r="40" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -3532,45 +3877,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>5004</v>
@@ -3588,12 +3933,12 @@
         <v>7647</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26" t="n">
@@ -3613,12 +3958,12 @@
         <v>0.0276844510146486</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B8" s="31" t="n">
         <v>1280</v>
@@ -3636,12 +3981,12 @@
         <v>2059</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">B8/B6</f>
@@ -3664,12 +4009,12 @@
         <v>0.26925591735321</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B10" s="31" t="n">
         <v>604</v>
@@ -3687,12 +4032,12 @@
         <v>913</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">B10/B6</f>
@@ -3715,12 +4060,12 @@
         <v>0.119393226101739</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B12" s="31" t="n">
         <v>425</v>
@@ -3738,12 +4083,12 @@
         <v>722</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B13" s="31" t="n">
         <v>225</v>
@@ -3761,12 +4106,12 @@
         <v>462</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B14" s="42" t="n">
         <v>0.55</v>
@@ -3784,12 +4129,12 @@
         <v>2.31</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">(F6/B6)^(1/4)-1</f>
@@ -3800,34 +4145,34 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="12" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B19" s="17" t="n">
         <v>0.44</v>
@@ -3840,12 +4185,12 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B20" s="17" t="n">
         <v>0.38</v>
@@ -3858,12 +4203,12 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B21" s="17" t="n">
         <v>0.18</v>
@@ -3876,12 +4221,12 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B22" s="30" t="n">
         <f aca="false">SUM(B19:B21)</f>
@@ -3895,27 +4240,27 @@
       <c r="E22" s="33"/>
       <c r="F22" s="33"/>
       <c r="G22" s="24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B25" s="17" t="n">
         <v>0.5</v>
@@ -3925,12 +4270,12 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B26" s="17" t="n">
         <v>0.5</v>
@@ -3940,212 +4285,212 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="12" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B30" s="14" t="n">
         <v>39</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B31" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B32" s="14" t="n">
         <v>44</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B33" s="17" t="n">
         <v>0.17</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B34" s="31" t="n">
         <v>370</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B35" s="31" t="n">
         <v>5600</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B36" s="31" t="n">
         <v>60000</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B37" s="31" t="n">
         <v>225000</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B38" s="37" t="n">
         <f aca="false">B30*B31*1000</f>
         <v>7800</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D38" s="33"/>
       <c r="E38" s="33"/>
       <c r="F38" s="33"/>
       <c r="G38" s="24" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B42" s="31" t="n">
         <v>1911</v>
@@ -4160,12 +4505,12 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B43" s="31" t="n">
         <v>520</v>
@@ -4180,12 +4525,12 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B44" s="31" t="n">
         <v>226</v>
@@ -4200,12 +4545,12 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B45" s="31" t="n">
         <v>113</v>
@@ -4220,12 +4565,12 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B46" s="17" t="n">
         <v>0.272</v>
@@ -4240,12 +4585,12 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="12" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B47" s="42" t="n">
         <v>0.72</v>
@@ -4260,31 +4605,31 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="12" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B50" s="31" t="n">
         <v>7800</v>
@@ -4299,12 +4644,12 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B51" s="31" t="n">
         <v>950</v>
@@ -4316,12 +4661,12 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B52" s="17" t="n">
         <v>0.122</v>
@@ -4333,68 +4678,68 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="12" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="12" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="12" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4424,54 +4769,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>22010</v>
@@ -4498,12 +4843,12 @@
         <v>31316</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26" t="n">
@@ -4535,12 +4880,12 @@
         <v>0.0180092321695597</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B8" s="31" t="n">
         <v>6458</v>
@@ -4567,12 +4912,12 @@
         <v>9708</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">B8/B6</f>
@@ -4607,12 +4952,12 @@
         <v>0.310001277302337</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31" t="n">
@@ -4637,12 +4982,12 @@
         <v>3243</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B11" s="31" t="n">
         <v>1402</v>
@@ -4669,12 +5014,12 @@
         <v>2789</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B11/B6</f>
@@ -4709,12 +5054,12 @@
         <v>0.089059905479627</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B13" s="31" t="n">
         <v>1108</v>
@@ -4741,41 +5086,41 @@
         <v>2006</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>0.24</v>
@@ -4795,12 +5140,12 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B18" s="17" t="n">
         <v>0.2</v>
@@ -4820,12 +5165,12 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B19" s="17" t="n">
         <v>0.16</v>
@@ -4845,12 +5190,12 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B20" s="17" t="n">
         <v>0.14</v>
@@ -4870,12 +5215,12 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B21" s="17" t="n">
         <v>0.13</v>
@@ -4895,12 +5240,12 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B22" s="17" t="n">
         <v>0.07</v>
@@ -4920,12 +5265,12 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>0.04</v>
@@ -4945,12 +5290,12 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>0.02</v>
@@ -4970,12 +5315,12 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B25" s="30" t="n">
         <f aca="false">SUM(B17:B24)</f>
@@ -4995,12 +5340,12 @@
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
       <c r="J25" s="24" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="17" t="n">
@@ -5015,12 +5360,12 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="12" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B27" s="33"/>
       <c r="C27" s="44" t="n">
@@ -5035,23 +5380,23 @@
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
       <c r="J27" s="24" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -5060,18 +5405,18 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B31" s="31" t="n">
         <v>31316</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -5080,19 +5425,19 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="12" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">E26*4</f>
         <v>1632</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -5101,19 +5446,19 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="12" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">B31-B32</f>
         <v>29684</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -5122,18 +5467,18 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B34" s="17" t="n">
         <v>0.22</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -5142,18 +5487,18 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="12" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B35" s="17" t="n">
         <v>0.24</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -5162,19 +5507,19 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="12" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B36" s="37" t="n">
         <f aca="false">B33*B34</f>
         <v>6530.48</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D36" s="33"/>
       <c r="E36" s="33"/>
@@ -5183,19 +5528,19 @@
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="J36" s="24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B37" s="37" t="n">
         <f aca="false">B33*B35</f>
         <v>7124.16</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D37" s="33"/>
       <c r="E37" s="33"/>
@@ -5204,19 +5549,19 @@
       <c r="H37" s="33"/>
       <c r="I37" s="33"/>
       <c r="J37" s="24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">B37/B31</f>
         <v>0.22749265551156</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -5225,23 +5570,23 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -5250,18 +5595,18 @@
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B42" s="17" t="n">
         <v>0.07</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -5270,18 +5615,18 @@
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="12" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B43" s="17" t="n">
         <v>0.15</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -5290,18 +5635,18 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="12" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B44" s="31" t="n">
         <v>1600</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -5310,18 +5655,18 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="12" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B45" s="31" t="n">
         <v>45</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -5330,18 +5675,18 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="12" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B46" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -5350,18 +5695,18 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
       <c r="J46" s="12" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B47" s="17" t="n">
         <v>0.095</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -5370,18 +5715,18 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
       <c r="J47" s="12" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B48" s="17" t="n">
         <v>0.098</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -5418,36 +5763,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B6" s="46" t="n">
         <f aca="false">'Core and Main'!F6</f>
@@ -5458,12 +5803,12 @@
         <v>31316</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B7" s="46" t="n">
         <f aca="false">'Core and Main'!F6</f>
@@ -5474,12 +5819,12 @@
         <v>7124.16</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">B7/B6</f>
@@ -5490,42 +5835,42 @@
         <v>0.22749265551156</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B9" s="46" t="n">
         <f aca="false">'Core and Main'!C19</f>
         <v>3364.68</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">B9/B6</f>
         <v>0.44</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B11" s="17" t="n">
         <v>0.122</v>
@@ -5534,43 +5879,43 @@
         <v>0.107</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B16" s="27" t="n">
         <f aca="false">B7+C7</f>
@@ -5578,12 +5923,12 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B17" s="46" t="n">
         <f aca="false">'Core and Main'!B30*1000</f>
@@ -5591,12 +5936,12 @@
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B18" s="30" t="n">
         <f aca="false">B16/B17</f>
@@ -5604,31 +5949,31 @@
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="24" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B22" s="43" t="n">
         <f aca="false">B9</f>
@@ -5639,12 +5984,12 @@
         <v>7124.16</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B23" s="13" t="n">
         <v>0.01</v>
@@ -5653,12 +5998,12 @@
         <v>0.01</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B24" s="27" t="n">
         <f aca="false">B22*B23</f>
@@ -5669,12 +6014,12 @@
         <v>71.2416</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B25" s="30" t="n">
         <f aca="false">B24/B6</f>
@@ -5685,12 +6030,12 @@
         <v>0.0022749265551156</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">B24*B11</f>
@@ -5701,26 +6046,26 @@
         <v>7.6228512</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B29" s="17" t="n">
         <v>0.0125</v>
@@ -5729,12 +6074,12 @@
         <v>0.0125</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B30" s="30" t="n">
         <f aca="false">B22*B29/B6</f>
@@ -5745,12 +6090,12 @@
         <v>0.0028436581938945</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -5786,380 +6131,380 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B6" s="47" t="n">
         <f aca="false">'Historical Spending'!B10</f>
         <v>114</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B7" s="46" t="n">
         <f aca="false">'Historical Spending'!B7</f>
         <v>0.023</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B8" s="46" t="n">
         <f aca="false">'Historical Spending'!B8</f>
         <v>175</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B9" s="47" t="n">
         <f aca="false">'Historical Spending'!B44</f>
         <v>6.4</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B13" s="23" t="n">
         <f aca="false">Assumptions!B6</f>
         <v>68</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">'Forward Model'!G9</f>
         <v>82.3912648425</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">'Forward Model'!L9</f>
         <v>97.3544695481693</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B16" s="47" t="n">
         <f aca="false">('Forward Model'!L9/'Forward Model'!C9)^(1/9)-1</f>
         <v>0.0406778986328729</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B17" s="47" t="n">
         <f aca="false">Assumptions!B11</f>
         <v>0.0985294117647059</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B18" s="23" t="n">
         <f aca="false">Scenarios!L5</f>
         <v>81.2245765003887</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">Scenarios!L7</f>
         <v>109.398410585824</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B23" s="48" t="n">
         <f aca="false">'Pipe and Assets'!B24</f>
         <v>9.86206896551724</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B24" s="47" t="n">
         <f aca="false">'Pipe and Assets'!B23</f>
         <v>-0.207142857142857</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B25" s="46" t="str">
         <f aca="false">Regulatory!B5</f>
         <v>Value</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">Regulatory!B11</f>
         <v>15</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B30" s="46" t="n">
         <f aca="false">Comparison!B6</f>
         <v>7647</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B31" s="46" t="n">
         <f aca="false">Comparison!C6</f>
         <v>31316</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B32" s="47" t="n">
         <f aca="false">Comparison!B18</f>
         <v>0.378747692307692</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B33" s="47" t="n">
         <f aca="false">Comparison!B25</f>
         <v>0.0044</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B34" s="47" t="n">
         <f aca="false">Comparison!C25</f>
         <v>0.0022749265551156</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D34" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -6174,6 +6519,543 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFA8451C"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>767</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>769</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>770</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="12" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="12" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="12" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="12" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="12" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="12" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="12" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="12" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="12" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="12" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="12" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="12" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>864</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF5C6E7C"/>
@@ -6189,396 +7071,396 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>753</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>754</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>755</v>
+        <v>867</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>757</v>
+        <v>868</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>759</v>
+        <v>870</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>760</v>
+        <v>871</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>761</v>
+        <v>872</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>762</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>763</v>
+        <v>874</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>764</v>
+        <v>875</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>765</v>
+        <v>876</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>766</v>
+        <v>877</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>767</v>
+        <v>878</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>768</v>
+        <v>879</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>769</v>
+        <v>880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>770</v>
+        <v>881</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>771</v>
+        <v>882</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>772</v>
+        <v>883</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>757</v>
+        <v>868</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>759</v>
+        <v>870</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>773</v>
+        <v>884</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>774</v>
+        <v>885</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>775</v>
+        <v>886</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>776</v>
+        <v>887</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>777</v>
+        <v>888</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>778</v>
+        <v>889</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>779</v>
+        <v>890</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>780</v>
+        <v>891</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>781</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>782</v>
+        <v>893</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>783</v>
+        <v>894</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>784</v>
+        <v>895</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>785</v>
+        <v>896</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>786</v>
+        <v>897</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>787</v>
+        <v>898</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>757</v>
+        <v>868</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>759</v>
+        <v>870</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>788</v>
+        <v>899</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>789</v>
+        <v>900</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>790</v>
+        <v>901</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>791</v>
+        <v>902</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>792</v>
+        <v>903</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>793</v>
+        <v>904</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>794</v>
+        <v>905</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>795</v>
+        <v>906</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>796</v>
+        <v>907</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>797</v>
+        <v>908</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>798</v>
+        <v>909</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>799</v>
+        <v>910</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>800</v>
+        <v>911</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>801</v>
+        <v>912</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>802</v>
+        <v>913</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>803</v>
+        <v>914</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>804</v>
+        <v>915</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>805</v>
+        <v>916</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>806</v>
+        <v>917</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>807</v>
+        <v>918</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>808</v>
+        <v>919</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>809</v>
+        <v>920</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>810</v>
+        <v>921</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>811</v>
+        <v>922</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>812</v>
+        <v>923</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>813</v>
+        <v>924</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>814</v>
+        <v>925</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>757</v>
+        <v>868</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>759</v>
+        <v>870</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>815</v>
+        <v>926</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>816</v>
+        <v>927</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>817</v>
+        <v>928</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>818</v>
+        <v>929</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>819</v>
+        <v>930</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>820</v>
+        <v>931</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>821</v>
+        <v>932</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>822</v>
+        <v>933</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>823</v>
+        <v>934</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>824</v>
+        <v>935</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>825</v>
+        <v>936</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6588,133 +7470,133 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>757</v>
+        <v>868</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>759</v>
+        <v>870</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>826</v>
+        <v>937</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>827</v>
+        <v>938</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>828</v>
+        <v>939</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>829</v>
+        <v>940</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>830</v>
+        <v>941</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>831</v>
+        <v>942</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>832</v>
+        <v>943</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>833</v>
+        <v>944</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>834</v>
+        <v>945</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>835</v>
+        <v>946</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>836</v>
+        <v>947</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>837</v>
+        <v>948</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>838</v>
+        <v>949</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>839</v>
+        <v>950</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>785</v>
+        <v>896</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>840</v>
+        <v>951</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>841</v>
+        <v>952</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>757</v>
+        <v>868</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>759</v>
+        <v>870</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>842</v>
+        <v>953</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>843</v>
+        <v>954</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>844</v>
+        <v>955</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>845</v>
+        <v>956</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>846</v>
+        <v>957</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>847</v>
+        <v>958</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6722,13 +7604,13 @@
         <v>31</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>848</v>
+        <v>959</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>849</v>
+        <v>960</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>850</v>
+        <v>961</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6736,13 +7618,13 @@
         <v>31</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>851</v>
+        <v>962</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>852</v>
+        <v>963</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>853</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -6778,136 +7660,136 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>68</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>0.045</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>8.7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">B8-B9</f>
         <v>6.7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">B10/B6</f>
         <v>0.0985294117647059</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>0.03</v>
@@ -6921,7 +7803,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="20" t="n">
         <f aca="false">B7</f>
@@ -6937,7 +7819,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>0.055</v>
@@ -6951,58 +7833,58 @@
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>0</v>
@@ -7037,10 +7919,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>0</v>
@@ -7075,10 +7957,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>0</v>
@@ -7113,17 +7995,17 @@
     </row>
     <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -7153,58 +8035,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C5" s="23" t="n">
         <f aca="false">Assumptions!$B$6*(1+Assumptions!$B$7)^0</f>
@@ -7249,10 +8131,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C6" s="23" t="n">
         <f aca="false">-Assumptions!$B$10*Assumptions!C$23</f>
@@ -7297,10 +8179,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" s="23" t="n">
         <f aca="false">Assumptions!C$24</f>
@@ -7345,10 +8227,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="23" t="n">
         <f aca="false">Assumptions!C$25</f>
@@ -7393,10 +8275,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">SUM(C5:C8)</f>
@@ -7441,10 +8323,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26" t="n">
@@ -7486,24 +8368,24 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">SUM(D9:L9)</f>
@@ -7511,12 +8393,12 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">(L9/C9)^(1/9)-1</f>
@@ -7524,12 +8406,12 @@
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B16" s="7" t="str">
         <f aca="false">INDEX($C$4:$L$4,MATCH(MIN(D10:L10),D10:L10,0)+1)</f>
@@ -7537,12 +8419,12 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">MIN(D10:L10)</f>
@@ -7550,12 +8432,12 @@
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7590,53 +8472,53 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C5" s="23" t="n">
         <f aca="false">Assumptions!$B$6*(1+Assumptions!$B$15)^0-Assumptions!$C$15*Assumptions!C$23+Assumptions!$D$15*(Assumptions!C$24+Assumptions!C$25)</f>
@@ -7681,10 +8563,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C6" s="28" t="n">
         <f aca="false">Assumptions!$B$6*(1+Assumptions!$B$16)^0-Assumptions!$C$16*Assumptions!C$23+Assumptions!$D$16*(Assumptions!C$24+Assumptions!C$25)</f>
@@ -7729,10 +8611,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C7" s="23" t="n">
         <f aca="false">Assumptions!$B$6*(1+Assumptions!$B$17)^0-Assumptions!$C$17*Assumptions!C$23+Assumptions!$D$17*(Assumptions!C$24+Assumptions!C$25)</f>
@@ -7777,48 +8659,48 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="29" t="n">
         <f aca="false">C7-C5</f>
@@ -7863,10 +8745,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" s="26" t="n">
         <f aca="false">C10/C5</f>
@@ -7911,26 +8793,26 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" s="15" t="n">
         <f aca="false">G5</f>
@@ -7947,7 +8829,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">G6</f>
@@ -7964,7 +8846,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="15" t="n">
         <f aca="false">G7</f>
@@ -7981,7 +8863,7 @@
     </row>
     <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -8016,605 +8898,605 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>626</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.023</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B8" s="31" t="n">
         <v>175</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="26" t="n">
         <f aca="false">B8/B6</f>
         <v>0.279552715654952</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B9" s="32" t="n">
         <v>59</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="26" t="n">
         <f aca="false">B9/B8</f>
         <v>0.337142857142857</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B10" s="31" t="n">
         <v>114</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="26" t="n">
         <f aca="false">B10/B8</f>
         <v>0.651428571428572</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B11" s="17" t="n">
         <v>0.92</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>0.08</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>0.567</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>0.79</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B18" s="14" t="n">
         <v>36.5</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>34.8</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>54.3</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>53</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B22" s="15" t="n">
         <f aca="false">B18+B20</f>
         <v>90.8</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B26" s="31" t="n">
         <v>350</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B27" s="29" t="n">
         <f aca="false">B26/13</f>
         <v>26.9230769230769</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B28" s="31" t="n">
         <v>226</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B29" s="29" t="n">
         <f aca="false">B28/13</f>
         <v>17.3846153846154</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B30" s="31" t="n">
         <v>279</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>197</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B31" s="31" t="n">
         <v>492</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B32" s="26" t="n">
         <f aca="false">B31/B30-1</f>
         <v>0.763440860215054</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B36" s="17" t="n">
         <v>0.051</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B37" s="17" t="n">
         <v>0.242</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B38" s="17" t="n">
         <v>0.06</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D38" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>210</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B39" s="17" t="n">
         <v>0.048</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D39" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>210</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>27.9</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B41" s="14" t="n">
         <v>39.9</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>216</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B42" s="17" t="n">
         <v>0.195</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B43" s="14" t="n">
         <v>6.75</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>218</v>
-      </c>
       <c r="E43" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B44" s="14" t="n">
         <v>6.4</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -8651,635 +9533,635 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>11.4</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>1.64</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>1.6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>235</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>2.6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>235</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>1.1</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>235</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>2.6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>235</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>3.04</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>11.7</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>11.7</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B22" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B23" s="14" t="n">
         <v>7.6</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">SUM(B19:B23)</f>
         <v>50</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">Assumptions!B8</f>
         <v>8.7</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B28/Assumptions!B6</f>
         <v>0.127941176470588</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B30" s="17" t="n">
         <v>0.67</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B31" s="15" t="n">
         <f aca="false">B30*B24</f>
         <v>33.5</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">Assumptions!B9</f>
         <v>2</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">Assumptions!B10</f>
         <v>6.7</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D33" s="33"/>
       <c r="E33" s="24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B34" s="34" t="n">
         <f aca="false">Assumptions!B11</f>
         <v>0.0985294117647059</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D34" s="33"/>
       <c r="E34" s="24" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B39" s="14" t="n">
         <v>51</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>11</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B41" s="14" t="n">
         <v>1.2</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B42" s="14" t="n">
         <v>0.682</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B43" s="17" t="n">
         <v>-0.16</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B44" s="14" t="n">
         <v>0.91</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B45" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B46" s="14" t="n">
         <v>14</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B47" s="14" t="n">
         <v>16.5</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B48" s="14" t="n">
         <v>0.065</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -9311,586 +10193,586 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>625</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D5" s="15" t="n">
         <f aca="false">B5/20</f>
         <v>31.25</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>630.1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D6" s="15" t="n">
         <f aca="false">B6/20</f>
         <v>31.505</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B7" s="31" t="n">
         <v>99</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">B7+Assumptions!B6</f>
         <v>167</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B8" s="31" t="n">
         <v>2250</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">B8/25</f>
         <v>90</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B12" s="15" t="n">
         <f aca="false">D5+D6</f>
         <v>62.755</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="12" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>0.045</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>4.5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B12*(1+B13)^B14</f>
         <v>76.5017977447615</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B19" s="31" t="n">
         <v>59</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B20" s="15" t="n">
         <f aca="false">B19*(1+B13)^3</f>
         <v>67.328801375</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>36.5</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B22" s="14" t="n">
         <v>54.3</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>0.65</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B24" s="15" t="n">
         <f aca="false">(B21+B22*B23)*0.95</f>
         <v>68.20525</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B25" s="31" t="n">
         <v>30</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B26" s="15" t="n">
         <f aca="false">D8/2.68</f>
         <v>33.5820895522388</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B27" s="15" t="n">
         <f aca="false">B25+B26</f>
         <v>63.5820895522388</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B28" s="15" t="n">
         <f aca="false">AVERAGE(B20,B24)</f>
         <v>67.7670256875</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B29" s="15" t="n">
         <f aca="false">AVERAGE(B20,B24,B27)</f>
         <v>66.3720469757463</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B30" s="15" t="n">
         <f aca="false">MIN(B20,B24,B27)</f>
         <v>63.5820895522388</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">MAX(B20,B24,B27)</f>
         <v>68.20525</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B31" s="35" t="n">
         <f aca="false">Assumptions!B6</f>
         <v>68</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" s="33"/>
       <c r="E31" s="24" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B32" s="16" t="n">
         <f aca="false">Assumptions!B6/B29-1</f>
         <v>0.0245276904725966</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B33" s="15" t="n">
         <f aca="false">B15-Assumptions!B6</f>
         <v>8.50179774476149</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B34" s="16" t="n">
         <f aca="false">B33/Assumptions!B6</f>
         <v>0.125026437422963</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>515.4</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B41" s="14" t="n">
         <v>37.2</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B42" s="14" t="n">
         <v>57.3</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B43" s="14" t="n">
         <v>310.4</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B44" s="14" t="n">
         <v>406.4</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B45" s="14" t="n">
         <v>99.3</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -9920,132 +10802,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>802</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="12" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B8" s="31" t="n">
         <v>400000</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B9" s="36" t="n">
         <v>2023</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>28.6</v>
@@ -10061,12 +10943,12 @@
         <v>0.86</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B16" s="14" t="n">
         <v>10.3</v>
@@ -10082,12 +10964,12 @@
         <v>0.41</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>9.2</v>
@@ -10101,12 +10983,12 @@
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="12" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B18" s="14" t="n">
         <v>5.1</v>
@@ -10120,12 +11002,12 @@
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>2.9</v>
@@ -10139,12 +11021,12 @@
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="12" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="37" t="n">
@@ -10157,12 +11039,12 @@
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="24" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>11.1</v>
@@ -10171,12 +11053,12 @@
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B22" s="14" t="n">
         <v>14</v>
@@ -10185,12 +11067,12 @@
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">B21/B22-1</f>
@@ -10200,12 +11082,12 @@
       <c r="D23" s="33"/>
       <c r="E23" s="33"/>
       <c r="F23" s="24" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B24" s="38" t="n">
         <f aca="false">B15/B19</f>
@@ -10215,387 +11097,387 @@
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
       <c r="F24" s="24" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B28" s="31" t="n">
         <v>2200000</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B29" s="31" t="n">
         <v>50000</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B30" s="31" t="n">
         <v>800000</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B31" s="31" t="n">
         <v>17544</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B32" s="17" t="n">
         <v>0.81</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="12" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B33" s="17" t="n">
         <v>0.15</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="12" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B34" s="17" t="n">
         <v>0.33</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B35" s="17" t="n">
         <v>0.194</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="12" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B36" s="31" t="n">
         <v>53</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B37" s="31" t="n">
         <v>452</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="12" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B38" s="31" t="n">
         <v>260000</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="12" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B39" s="14" t="n">
         <v>2.6</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B40" s="31" t="n">
         <v>860</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B41" s="31" t="n">
         <v>850</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B42" s="39" t="n">
         <f aca="false">B39*1000000000/B38</f>
         <v>10000</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="12" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B46" s="31" t="n">
         <v>140</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B47" s="31" t="n">
         <v>127</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B48" s="31" t="n">
         <v>88</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B49" s="31" t="n">
         <v>82</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B50" s="31" t="n">
         <v>322</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>459</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>457</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="12" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -10627,462 +11509,462 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>9200000</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B7" s="40" t="n">
         <v>4700</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B8" s="40" t="n">
         <v>6930</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">B6*B7/1000000000</f>
         <v>43.24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">B6*B8/1000000000</f>
         <v>63.756</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">AVERAGE(B9:B10)-B11</f>
         <v>38.498</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="41" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B19" s="31" t="n">
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="6"/>
       <c r="D22" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="6"/>
       <c r="D23" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B24" s="31" t="n">
         <v>50</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B25" s="14" t="n">
         <v>3.5</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B26" s="40" t="n">
         <v>305</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B27" s="40" t="n">
         <v>3570</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B33" s="31" t="n">
         <v>860</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B34" s="31" t="n">
         <v>850</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B35" s="31" t="n">
         <v>40</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B36" s="31" t="n">
         <v>18</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B37" s="31" t="n">
         <v>85</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
